--- a/Extracted_data_analysis/tropical/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
+++ b/Extracted_data_analysis/tropical/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">meso_substrate</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">taxonomy</t>
   </si>
   <si>
     <t xml:space="preserve">Behaviour</t>
@@ -591,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C2" t="n">
-        <v>71.04</v>
+        <v>71.39</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +602,7 @@
         <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>19.55</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="4">
@@ -616,7 +613,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="5">
@@ -627,7 +624,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +635,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
     </row>
   </sheetData>
@@ -668,10 +665,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>16.97</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="3">
@@ -682,7 +679,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>8.6</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="4">
@@ -690,10 +687,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C4" t="n">
-        <v>73.98</v>
+        <v>73.93</v>
       </c>
     </row>
   </sheetData>
@@ -726,7 +723,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="3">
@@ -734,10 +731,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C3" t="n">
-        <v>97.51</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="4">
@@ -748,7 +745,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="5">
@@ -770,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -800,10 +797,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C2" t="n">
-        <v>94.57</v>
+        <v>94.38</v>
       </c>
     </row>
     <row r="3">
@@ -811,10 +808,10 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>14.71</v>
+        <v>14.83</v>
       </c>
     </row>
   </sheetData>
@@ -844,10 +841,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>26.47</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="3">
@@ -855,10 +852,10 @@
         <v>21</v>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C3" t="n">
-        <v>44.57</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="4">
@@ -866,10 +863,10 @@
         <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="n">
-        <v>20.59</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="5">
@@ -880,7 +877,7 @@
         <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>23.53</v>
+        <v>23.37</v>
       </c>
     </row>
   </sheetData>
@@ -910,10 +907,10 @@
         <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>20.81</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="3">
@@ -921,10 +918,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>30.32</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="4">
@@ -932,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" t="n">
-        <v>40.5</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="5">
@@ -943,10 +940,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>12.67</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="6">
@@ -954,7 +951,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
         <v>32.13</v>
@@ -968,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -979,7 +976,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>15.84</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="9">
@@ -990,7 +987,7 @@
         <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>27.15</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="10">
@@ -1001,7 +998,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>8.14</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="11">
@@ -1009,10 +1006,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>20.14</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="12">
@@ -1023,7 +1020,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>5.88</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="13">
@@ -1034,7 +1031,7 @@
         <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>8.37</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1053,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="16">
@@ -1067,7 +1064,7 @@
         <v>94</v>
       </c>
       <c r="C16" t="n">
-        <v>21.27</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="17">
@@ -1078,7 +1075,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="18">
@@ -1089,7 +1086,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="19">
@@ -1097,10 +1094,10 @@
         <v>42</v>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1108,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="21">
@@ -1119,10 +1116,10 @@
         <v>44</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>6.11</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="22">
@@ -1130,10 +1127,10 @@
         <v>45</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.23</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="23">
@@ -1141,10 +1138,10 @@
         <v>46</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1152,10 +1149,10 @@
         <v>47</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -1163,10 +1160,10 @@
         <v>48</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="26">
@@ -1174,10 +1171,10 @@
         <v>49</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="27">
@@ -1185,10 +1182,10 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="28">
@@ -1196,10 +1193,10 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="29">
@@ -1207,21 +1204,10 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1223,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1248,68 +1234,68 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>33.48</v>
+        <v>33.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" t="n">
         <v>127</v>
       </c>
       <c r="C3" t="n">
-        <v>28.73</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C4" t="n">
-        <v>68.1</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="n">
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="n">
         <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>13.12</v>
+        <v>13.03</v>
       </c>
     </row>
   </sheetData>
@@ -1325,7 +1311,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1336,35 +1322,35 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C2" t="n">
-        <v>85.75</v>
+        <v>85.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" t="n">
         <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>9.95</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="5">
@@ -1375,122 +1361,122 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" t="n">
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" t="n">
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" t="n">
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>7.47</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
